--- a/题库/PY程序设计模拟题5.xlsx
+++ b/题库/PY程序设计模拟题5.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下面代码的输出结果是（）。</t>
     </r>
     <r>
@@ -107,6 +113,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下面代码的输出结果是</t>
     </r>
     <r>
@@ -150,6 +162,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下面代码的输出结果是（）。</t>
     </r>
     <r>
@@ -185,6 +203,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>执行下列语句后的显示结果是（）。</t>
     </r>
     <r>
@@ -423,6 +447,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>[1]&gt; 
 [2] and 
 [3]b&gt;a</t>
@@ -1596,7 +1626,7 @@
       </c>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" ht="34" spans="1:10">
+    <row r="4" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4"/>
@@ -1698,7 +1728,7 @@
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" ht="51" spans="1:10">
+    <row r="8" spans="1:10">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="5"/>
@@ -1710,7 +1740,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" ht="34" spans="1:10">
+    <row r="9" spans="1:10">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="4"/>
@@ -1782,7 +1812,7 @@
       </c>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" ht="17" spans="1:10">
+    <row r="12" spans="1:10">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="5"/>
@@ -1794,7 +1824,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" ht="34" spans="1:10">
+    <row r="13" spans="1:10">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="5"/>
@@ -1848,7 +1878,7 @@
       </c>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" ht="68" spans="1:10">
+    <row r="16" spans="1:10">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="5"/>
@@ -1860,7 +1890,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" ht="34" spans="1:10">
+    <row r="17" spans="1:10">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="5"/>
@@ -1914,7 +1944,7 @@
       </c>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" ht="34" spans="1:10">
+    <row r="20" spans="1:10">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="5"/>
@@ -1926,7 +1956,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" ht="51" spans="1:10">
+    <row r="21" spans="1:10">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="4"/>
